--- a/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
+++ b/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T12:46:56+00:00</t>
+    <t>2026-07-01T13:09:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
+++ b/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:09:52+00:00</t>
+    <t>2026-07-02T10:13:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
+++ b/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T10:13:10+00:00</t>
+    <t>2026-07-02T12:53:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
+++ b/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T12:53:44+00:00</t>
+    <t>2026-07-02T13:05:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
+++ b/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T13:05:16+00:00</t>
+    <t>2026-07-02T13:38:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
+++ b/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T13:38:57+00:00</t>
+    <t>2026-07-02T14:02:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
+++ b/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T14:02:37+00:00</t>
+    <t>2026-07-02T14:16:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
+++ b/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T14:16:33+00:00</t>
+    <t>2026-07-02T15:12:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
+++ b/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T15:12:46+00:00</t>
+    <t>2026-07-08T12:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
+++ b/add-req-fhir-dmp/ig/StructureDefinition-SubmissionSet.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T12:59:55+00:00</t>
+    <t>2026-07-08T13:05:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
